--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486322_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486322_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5474</v>
+        <v>6.8566</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5796</v>
+        <v>5.0027</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9677</v>
+        <v>1.8539</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7523</v>
+        <v>7.4332</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1921</v>
+        <v>4.5622</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5602</v>
+        <v>2.8711</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6769</v>
+        <v>7.6104</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9923</v>
+        <v>5.2955</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6846</v>
+        <v>2.3149</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9246</v>
+        <v>-0.1771</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8003</v>
+        <v>-0.7333</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1243</v>
+        <v>0.5562</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2626</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R2" t="n">
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0326</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.6549</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8053</v>
+        <v>-0.6459</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.5857</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4314</v>
+        <v>6.01</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9002</v>
+        <v>5.3813</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5312</v>
+        <v>0.6287</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.322</v>
+        <v>2.7523</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7029</v>
+        <v>1.1921</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3809</v>
+        <v>1.5602</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1664</v>
+        <v>3.6769</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.9696</v>
+        <v>1.9923</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8032</v>
+        <v>1.6846</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1556</v>
+        <v>-0.9246</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7333</v>
+        <v>-0.8003</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4224</v>
+        <v>-0.1243</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0875</v>
+        <v>3.2626</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>3.2626</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7556</v>
+        <v>-0.5699</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3313</v>
+        <v>0.5744</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5757</v>
+        <v>-1.1443</v>
       </c>
       <c r="V3" t="n">
-        <v>4.9103</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>4.9103</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2361</v>
+        <v>4.708</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4439</v>
+        <v>3.5158</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7922</v>
+        <v>1.1921</v>
       </c>
       <c r="G4" t="n">
-        <v>7.4332</v>
+        <v>-1.322</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5622</v>
+        <v>-1.7029</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8711</v>
+        <v>0.3809</v>
       </c>
       <c r="J4" t="n">
-        <v>7.6104</v>
+        <v>-0.1664</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2955</v>
+        <v>-0.9696</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3149</v>
+        <v>0.8032</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1771</v>
+        <v>-1.1556</v>
       </c>
       <c r="N4" t="n">
         <v>-0.7333</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5562</v>
+        <v>-0.4224</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
         <v>3.2626</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0321</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0961</v>
+        <v>0.947</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7076</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5857</v>
+        <v>4.9103</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.9103</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9336</v>
+        <v>2.5991</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9674</v>
+        <v>4.1947</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0338</v>
+        <v>-1.5956</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9278999999999999</v>
+        <v>2.7298</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1917</v>
+        <v>1.0978</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1196</v>
+        <v>1.632</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7151999999999999</v>
+        <v>3.4831</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6387</v>
+        <v>2.4272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>1.0559</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2127</v>
+        <v>-0.7532</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8304</v>
+        <v>-1.3293</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0431</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3309</v>
+        <v>-0.4804</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6872</v>
+        <v>0.1466</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3563</v>
+        <v>-0.627</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1952</v>
+        <v>-0.9554</v>
       </c>
       <c r="W5" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7602</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7675</v>
+        <v>2.0386</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4556</v>
+        <v>1.9183</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6881</v>
+        <v>0.1203</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7298</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0978</v>
+        <v>-0.1917</v>
       </c>
       <c r="I6" t="n">
-        <v>1.632</v>
+        <v>1.1196</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4831</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4272</v>
+        <v>0.6387</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0559</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7532</v>
+        <v>0.2127</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3293</v>
+        <v>-0.8304</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5760999999999999</v>
+        <v>1.0431</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3119</v>
+        <v>0.4359</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5924</v>
+        <v>0.6381</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7195</v>
+        <v>-0.2022</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9554</v>
+        <v>-0.1952</v>
       </c>
       <c r="W6" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5204</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2882</v>
+        <v>-0.5242</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5337</v>
+        <v>0.2669</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8219</v>
+        <v>-0.7911</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3416</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0119</v>
+        <v>-0.2478</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2656</v>
+        <v>-0.0012</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2775</v>
+        <v>-0.2466</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8165</v>
+        <v>-2.1036</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6814</v>
+        <v>-1.1226</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1351</v>
+        <v>-0.981</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3783</v>
@@ -1078,13 +1078,13 @@
         <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1783</v>
+        <v>-0.4654</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4248</v>
+        <v>-0.2707</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5839</v>
+        <v>-3.4488</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2515</v>
+        <v>-4.3322</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6676</v>
+        <v>0.8834</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2427</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1682</v>
+        <v>-1.0332</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8099</v>
+        <v>0.1094</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3583</v>
+        <v>-1.1425</v>
       </c>
       <c r="V9" t="n">
         <v>0.7395</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7156</v>
+        <v>-3.5796</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5036</v>
+        <v>-2.4293</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.212</v>
+        <v>-1.1504</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7397</v>
@@ -1234,13 +1234,13 @@
         <v>3.4801</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.456</v>
+        <v>-1.3201</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>0.3569</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.7386</v>
+        <v>-1.677</v>
       </c>
       <c r="V10" t="n">
         <v>-2.8249</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7081</v>
+        <v>-6.0674</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0181</v>
+        <v>-7.2849</v>
       </c>
       <c r="F11" t="n">
-        <v>1.31</v>
+        <v>1.2175</v>
       </c>
       <c r="G11" t="n">
         <v>-4.297</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1114</v>
+        <v>-0.2478</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2752</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1198</v>
+        <v>0.0273</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.803699999999999</v>
+        <v>6.488700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.425800000000002</v>
+        <v>5.1107</v>
       </c>
       <c r="F12" t="n">
         <v>1.3778</v>
       </c>
       <c r="G12" t="n">
-        <v>1.521899999999999</v>
+        <v>1.5219</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6575</v>
+        <v>-1.657500000000001</v>
       </c>
       <c r="I12" t="n">
         <v>3.1795</v>
       </c>
       <c r="J12" t="n">
-        <v>7.3169</v>
+        <v>7.316899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>7.240999999999999</v>
+        <v>7.241</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07600000000000007</v>
+        <v>0.07600000000000096</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.794700000000001</v>
+        <v>-5.7947</v>
       </c>
       <c r="N12" t="n">
         <v>-8.898300000000001</v>
@@ -1390,16 +1390,16 @@
         <v>20.6631</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.5724</v>
+        <v>-3.8876</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2713</v>
+        <v>2.9562</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.8438</v>
+        <v>-6.8437</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1538000000000008</v>
+        <v>0.1538000000000004</v>
       </c>
       <c r="W12" t="n">
         <v>6.8005</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6522</v>
+        <v>3.9528</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1827</v>
+        <v>3.7298</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4696</v>
+        <v>0.223</v>
       </c>
       <c r="G13" t="n">
         <v>2.256</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1787</v>
+        <v>1.4793</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5813</v>
+        <v>1.1284</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5975</v>
+        <v>0.3509</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7922</v>
+        <v>1.7035</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5194</v>
+        <v>2.7371</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7273</v>
+        <v>-1.0337</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9724</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>0.877</v>
+        <v>0.7883</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6427</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7657</v>
+        <v>-0.0721</v>
       </c>
       <c r="V14" t="n">
         <v>4.7151</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8512999999999999</v>
+        <v>1.4549</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0503</v>
+        <v>0.739</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9016</v>
+        <v>0.7159</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.1868</v>
       </c>
       <c r="H15" t="n">
-        <v>0.523</v>
+        <v>0.8579</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4287</v>
+        <v>-1.0447</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2474</v>
+        <v>0.1025</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2045</v>
+        <v>0.8093</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4519</v>
+        <v>-0.7068</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3417</v>
+        <v>-0.2893</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6814</v>
+        <v>0.0486</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0231</v>
+        <v>-0.3379</v>
       </c>
       <c r="P15" t="n">
-        <v>0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R15" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1131</v>
+        <v>0.6868</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1971</v>
+        <v>0.7691</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3102</v>
+        <v>-0.0823</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4991</v>
+        <v>0.4852</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1551</v>
+        <v>-0.3856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6542</v>
+        <v>0.8708</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1868</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8579</v>
+        <v>0.523</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0447</v>
+        <v>-0.4287</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1025</v>
+        <v>-0.2474</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8093</v>
+        <v>1.2045</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7068</v>
+        <v>-1.4519</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2893</v>
+        <v>0.3417</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0486</v>
+        <v>-0.6814</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3379</v>
+        <v>1.0231</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2689</v>
+        <v>-0.4792</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.125</v>
+        <v>-0.1382</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.144</v>
+        <v>-0.341</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0337</v>
+        <v>0.1047</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1954</v>
+        <v>-1.2034</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1617</v>
+        <v>1.3081</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1197</v>
+        <v>-0.0999</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6759</v>
+        <v>0.073</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5563</v>
+        <v>-0.1729</v>
       </c>
       <c r="J17" t="n">
-        <v>0.224</v>
+        <v>-0.2727</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5626</v>
+        <v>-0.1397</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7865</v>
+        <v>-0.1331</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3436</v>
+        <v>0.1728</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1134</v>
+        <v>0.2127</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7697000000000001</v>
+        <v>-0.0399</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7586000000000001</v>
+        <v>1.8359</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8857</v>
+        <v>1.1356</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.127</v>
+        <v>0.7003</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3252</v>
+        <v>-1.8488</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9331</v>
+        <v>-0.175</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6614</v>
+        <v>-0.4189</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7282</v>
+        <v>0.244</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9714</v>
+        <v>-0.1197</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1435</v>
+        <v>-1.6759</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8279</v>
+        <v>1.5563</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8632</v>
+        <v>0.224</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8249</v>
+        <v>-0.5626</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0382</v>
+        <v>0.7865</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1083</v>
+        <v>-0.3436</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6814</v>
+        <v>-1.1134</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7897</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1645</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.262</v>
+        <v>0.6621</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0974</v>
+        <v>-0.0448</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9692</v>
+        <v>-0.3435</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0975</v>
+        <v>-1.1026</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1282</v>
+        <v>0.7591</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0999</v>
+        <v>1.9714</v>
       </c>
       <c r="H19" t="n">
-        <v>0.073</v>
+        <v>1.1435</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1729</v>
+        <v>0.8279</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2727</v>
+        <v>1.8632</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1397</v>
+        <v>1.8249</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1331</v>
+        <v>0.0382</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1728</v>
+        <v>0.1083</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2127</v>
+        <v>-0.6814</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0399</v>
+        <v>0.7897</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.762</v>
+        <v>0.4251</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2415</v>
+        <v>0.2968</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5204</v>
+        <v>0.1283</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8488</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.8488</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4268</v>
+        <v>-2.1108</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.293</v>
+        <v>-1.0695</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1338</v>
+        <v>-1.0413</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0584</v>
@@ -2014,13 +2014,13 @@
         <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4983</v>
+        <v>-0.1824</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.262</v>
+        <v>-0.0384</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.189</v>
+        <v>-2.7901</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4529</v>
+        <v>-0.8057</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7361</v>
+        <v>-1.9844</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6722</v>
+        <v>0.84</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5963000000000001</v>
+        <v>0.5962</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0758</v>
+        <v>0.2438</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3316</v>
+        <v>0.9788</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3864</v>
+        <v>0.8641</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.718</v>
+        <v>0.1147</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3406</v>
+        <v>-0.1388</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9827</v>
+        <v>-0.2679</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3578</v>
+        <v>0.1291</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3956</v>
+        <v>0.3476</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.3906</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5706</v>
+        <v>-0.043</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2835</v>
+        <v>-2.9039</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2527</v>
+        <v>-1.6765</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0307</v>
+        <v>-1.2274</v>
       </c>
       <c r="G22" t="n">
-        <v>0.84</v>
+        <v>-2.6722</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5962</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2438</v>
+        <v>-2.0758</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9788</v>
+        <v>-1.3316</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8641</v>
+        <v>0.3864</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1147</v>
+        <v>-1.718</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1388</v>
+        <v>-1.3406</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2679</v>
+        <v>-0.9827</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1291</v>
+        <v>-0.3578</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1458</v>
+        <v>0.6808</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0565</v>
+        <v>0.7427</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0893</v>
+        <v>-0.0619</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7632</v>
+        <v>-2.9463</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9216</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8416</v>
+        <v>-1.0247</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5745</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2088</v>
+        <v>0.6081</v>
       </c>
       <c r="T23" t="n">
         <v>1.0347</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2435</v>
+        <v>-0.4266</v>
       </c>
       <c r="V23" t="n">
         <v>0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.803699999999999</v>
+        <v>-3.5685</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.377799999999999</v>
+        <v>-1.3779</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.425999999999999</v>
+        <v>-2.1906</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5222</v>
@@ -2314,7 +2314,7 @@
         <v>-7.240900000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.07599999999999973</v>
+        <v>-0.07600000000000018</v>
       </c>
       <c r="P24" t="n">
         <v>-8.7003</v>
@@ -2326,13 +2326,13 @@
         <v>11.9626</v>
       </c>
       <c r="S24" t="n">
-        <v>4.572499999999999</v>
+        <v>6.8077</v>
       </c>
       <c r="T24" t="n">
-        <v>6.8437</v>
+        <v>6.8438</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.2714</v>
+        <v>-0.03609999999999985</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1540000000000002</v>
@@ -2341,7 +2341,7 @@
         <v>6.6466</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.800599999999999</v>
+        <v>-6.8006</v>
       </c>
     </row>
   </sheetData>
